--- a/output/pdf_financials_xlsx/LTX.xlsx
+++ b/output/pdf_financials_xlsx/LTX.xlsx
@@ -1038,7 +1038,7 @@
         <v>1.263991</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.222063</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.093819</v>
@@ -1047,13 +1047,13 @@
         <v>0.116648</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.092295</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.084158</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>0.06164</v>
       </c>
     </row>
     <row r="11">
@@ -2693,46 +2693,46 @@
         <v>0.007481</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>0.007481</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>0.64663</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.009159</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000725</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.009745999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.008267999999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.007872000000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.052103</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005234</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000151</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.001051</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.196525</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.079862</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.0006980000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2813,46 +2813,46 @@
         <v>0.007481</v>
       </c>
       <c r="E36" s="3" t="n">
+        <v>0.007481</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>0.64663</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.009159</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000725</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.009745999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.008267999999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.007872000000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.052103</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005234</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000151</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.001051</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.196525</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.079862</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.0006980000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3536,43 +3536,43 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.64663</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.009159</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.000725</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.014008</v>
+        <v>0.004262</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.008491</v>
+        <v>0.000223</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.008095</v>
+        <v>0.000223</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.060335</v>
+        <v>0.008232</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.008387</v>
+        <v>0.003153</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.026051</v>
+        <v>0.025</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.196525</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.079862</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.0006980000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -33886,7 +33886,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
